--- a/thermal-lunchbox-blog/保溫保鮮餐具_KW分類_2026-10-28.xlsx
+++ b/thermal-lunchbox-blog/保溫保鮮餐具_KW分類_2026-10-28.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Blog KW 重整'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'類別總覽'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'新增KW（GKP 已查）'!$A$1:$H$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'產品對照表'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'產品對照表'!$A$1:$K$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27487,18 +27487,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27514,35 +27516,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>型號</t>
+          <t>產品名稱（網店官方原文）</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>型號／貨號</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>容量／尺寸</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>重點規格</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>價錢（HKD）</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>網店</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>產品連結</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>產品圖片網址</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
@@ -27561,35 +27573,45 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>SL-NC09-ST 不銹鋼保溫便當盒</t>
+          <t>象印 - 0.84L不銹鋼保溫飯壺 (並盛) SL-NC09 ST 銀色</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
+          <t>SL-NC09-ST</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
           <t>0.84L</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>不銹鋼；內盒（蓋除外）可微波；附筷子及袋</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>$299（原價 $428）</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>HKTVmall</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>https://www.hktvmall.com/p/H0569001_S_GJE-SL-NC09-ST</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>https://images.hktv-img.com/images/HKTV/12638/GJE-SL-NC09-ST_main_47297478_20200804155912_01_1200.jpg</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>價錢來自搜尋結果卡</t>
         </is>
@@ -27608,35 +27630,45 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>LXB-A100 (XC) 保溫便當盒</t>
+          <t>虎牌 - 真空保溫飯盒 LXB-A100 不銹鋼色 0.88L | 日式雙層保溫便當盒 | 不銹鋼食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫壼 | 附筷子湯匙</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
+          <t>LXB-A100 (XC)</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
           <t>0.88L（飯 0.5L＋餸 0.38L）</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>SUS304；6 小時後保持 50°C 以上</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>$348（原價 $488）</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>HKTVmall（Tiger 官方旗艦店）</t>
         </is>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>https://www.hktvmall.com/p/H5036001_S_LXB-A100-XC</t>
         </is>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/df12/c9bb/ad1d/VcMtgUYaVG20250424142658_1200.png</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -27651,35 +27683,45 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>JEE-800-DGY 保溫便當盒</t>
+          <t>800毫升保溫便當盒 (400毫升保溫食物罐+400毫升食物儲存盒)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
+          <t>JEE-800-DGY</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
           <t>800ml（食物罐 400ml＋保鮮盒 400ml）</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>6 小時保持 60°C 以上（連套及袋 62°C 以上）</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>$338</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>THERMOS HK 官網</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>https://www.thermos.com.hk/product/d004b821-b818-4163-b143-2421736cc46f</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/4jt453fJsHDBJXQi6jkPD.png</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -27694,35 +27736,45 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>JBT-400 燜燒罐</t>
+          <t>400毫升真空食物罐 - 藕粉</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
+          <t>JBT-400-MTPK</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
           <t>400ml</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>6 小時：熱 59°C 以上／冷 11°C 以下</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>$378</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>THERMOS HK 官網</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>https://www.thermos.com.hk/product/ba9dc661-65d6-4a80-9a22-31aff4eb8d96</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/OTxKkk94WVhg9k0HSwtUp.png</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -27737,35 +27789,45 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>SW-EAE50 燜燒杯</t>
+          <t>象印 - 0.5L不銹鋼真空飯壺 燜燒杯【香港行貨】SW-EAE50 AB 淺藍色</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
+          <t>SW-EAE50-AB</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
           <t>0.5L</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>6 小時：熱 64°C 以上／冷 10°C 以下；SUS304；口徑 6.5cm</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>$269（原價 $278）</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>HKTVmall</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>https://www.hktvmall.com/p/H0569001_S_GJE-SW-EAE50-AB</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-mms.hktvmall.com/hktv/mms/uploadProductImage/cc38/007a/9cbf/pyYJVLlwPu20220719123951_1200.jpg</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -27780,35 +27842,45 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>MCJ-K075 燜燒罐</t>
+          <t>虎牌 - 不銹鋼真空燜燒杯 MCJ-K075 750ml 犀牛灰 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
+          <t>MCJ-K075 (HC)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
           <t>0.75L</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>6 小時：熱 70°C 以上／冷 8°C 以下；口徑 7.8cm</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>$298（原價 $468）</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>HKTVmall（Tiger 官方旗艦店）</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>https://www.hktvmall.com/p/H5036001_S_MCJ-K075-HC</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/4781/e49e/b2c5/jxwZGMsQSN20250424145612_1200.png</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -27823,35 +27895,45 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>無線加熱飯盒 F72</t>
+          <t>Life Element 生活元素 無線加熱飯盒 F72 紫色</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
+          <t>F72</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
           <t>1L</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>50W；220V；可充電</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>$590（原價 $780）</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>友和 YOHO</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>https://www.yohohongkong.com/zh-hk/product/98338</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>https://store.yohohongkong.com/mkp/gallery/goods/images/1a83cb2b-7cc4-4b3f-af4a-9ca201760e25_mkp_image.jpg</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -27866,35 +27948,45 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>F-818 充電式電熱飯盒</t>
+          <t>Mercury 免插電充電式電熱飯盒 F-818 抹茶色</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
+          <t>F-818</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
           <t>1L</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>40W；3200mAh；Type-C；304 不銹鋼內膽</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>$425（原價 $530）</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>友和 YOHO</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>https://www.yohohongkong.com/zh-hk/product/188590</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>https://store.yohohongkong.com/mkp/gallery/goods/images/953c38eb-6a36-4878-951f-b649546c9fb0_mkp_image.webp</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -27909,35 +28001,45 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>充電式便攜加熱飯盒</t>
+          <t>VVU&amp;CCO 物克 充電式便攜加熱飯盒</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
+          <t>（頁面未列型號）</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
           <t>未有標示</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>可充電；多段溫度；內膽可拆</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>$415（原價 $510）</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>友和 YOHO</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>https://www.yohohongkong.com/zh-hk/product/492130</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>https://store.yohohongkong.com/mkp/gallery/goods/images/a3c71d28-845f-4c49-93da-ffd505ad7c8c_mkp_image.webp</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>頁面未列容量</t>
         </is>
@@ -27956,35 +28058,45 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>強化玻璃微波保鮮盒（長方形 2 件裝）</t>
+          <t>Glasslock 強化玻璃微波保鮮盒 櫻花粉晶透款 長方形 1020ml 兩個裝</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
+          <t>（頁面未列型號）</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
           <t>1020ml ×2</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>強化玻璃；盒身可微波、焗爐、洗碗碟機、冷藏</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>$285（原價 $371）</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>友和 YOHO</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>https://www.yohohongkong.com/zh-hk/product/114329</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>https://store.yohohongkong.com/mkp/gallery/goods/images/b38e68cb-27ad-4bec-ae50-0e1a2b24df8b_mkp_image.webp</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -27999,35 +28111,45 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>真空保鮮盒</t>
+          <t>Food Fresh 真空保鮮盒 避光儲存 |雙重技術 [保鮮]•[保質] | 密封 防漏｜防潮 防霉| ★2026新款★</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
+          <t>（頁面未列型號）</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
           <t>未能確認</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>抽真空保鮮</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>$245（原價 $378）</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>友和 YOHO</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>https://www.yohohongkong.com/zh-hk/product/116443</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>https://store.yohohongkong.com/mkp/gallery/goods/images/cb12567c-95ed-4878-b9f0-932baaec461c_mkp_image.webp</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>容量未能確認</t>
         </is>
@@ -28051,30 +28173,40 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
+          <t>4550583134433</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
           <t>0.99L</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>改性 PCT 盒身及蓋，矽膠密封圈</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>$38</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>MUJI 香港網店</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>https://onlineshop.muji.com.hk/products/4550583134433</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>https://img.shoplineapp.com/media/image_clips/67592bb20602cf000a92c393/original.jpg</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>可否微波頁面未有註明</t>
         </is>
@@ -28093,35 +28225,45 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>佳能保鮮紙 200 呎</t>
+          <t>佳能保鮮紙 200FT</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
+          <t>101343913（惠康貨號）</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
           <t>200 呎</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>一般保鮮紙</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>$23（原價 $25）</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>惠康 Wellcome</t>
         </is>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>https://www.wellcome.com.hk/zh-hant/p/%E4%BD%B3%E8%83%BD%E4%BF%9D%E9%AE%AE%E7%B4%99%20200FT/i/101343913.html</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>https://img.rtacdn-os.com/20260109/4c971e3e-bb2f-3030-b1f7-4164c2c2f2d7</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -28136,35 +28278,45 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>佳能保鮮魔術貼（Press'n Seal）</t>
+          <t>佳能保鮮魔術貼 30厘米 70呎</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
+          <t>115847548（惠康貨號）</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
           <t>30cm × 70 呎</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>可直接黏貼容器及碗碟；美國製</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>$36.9（原價 $41.9）</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>惠康 Wellcome</t>
         </is>
       </c>
-      <c r="H15" s="12" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>https://www.wellcome.com.hk/zh-hant/p/%E4%BD%B3%E8%83%BD%E4%BF%9D%E9%AE%AE%E9%AD%94%E8%A1%93%E8%B2%BC%2030%E5%8E%98%E7%B1%B3%2070%E5%91%8E/i/115847548.html</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>https://img.rtacdn-os.com/20260109/fe30dcb5-a06d-38ef-84a7-8511e6c45cc0</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -28179,35 +28331,45 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>佳能微波爐保鮮紙 100 呎</t>
+          <t>佳能微波爐保鮮紙 100FT</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
+          <t>101331506（惠康貨號）</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
           <t>100 呎</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>微波爐適用</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>$28.9（原價 $34）</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>惠康 Wellcome</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>https://www.wellcome.com.hk/zh-hant/p/%E4%BD%B3%E8%83%BD%E5%BE%AE%E6%B3%A2%E7%88%90%E4%BF%9D%E9%AE%AE%E7%B4%99%20100FT/i/101331506.html</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>https://img.rtacdn-os.com/20260109/29664bcc-009a-30f2-acbd-971b237d683b</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>價錢來自搜尋結果卡</t>
         </is>
@@ -28226,35 +28388,45 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>佳能雙重鎖緊密實袋（中）</t>
+          <t>佳能雙重鎖緊密實袋中 50PC</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
+          <t>101335749（惠康貨號）</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
           <t>50 個</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>雙重拉鏈</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>$26.8（原價 $34）</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>惠康 Wellcome</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>https://www.wellcome.com.hk/zh-hant/p/%E4%BD%B3%E8%83%BD%E9%9B%99%E9%87%8D%E9%8E%96%E7%B7%8A%E5%AF%86%E5%AF%A6%E8%A2%8B%E4%B8%AD%2050PC/i/101335749.html</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>https://img.rtacdn-os.com/20260109/322dcc3f-3cbe-3016-9fbf-8820980db771</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -28269,35 +28441,45 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>佳能食物保鮮袋（大）</t>
+          <t>佳能食物保鮮袋大袋 100EA</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
+          <t>101347619（惠康貨號）</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
           <t>100 個</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>一般食物保鮮袋</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>$16</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>惠康 Wellcome</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>https://www.wellcome.com.hk/zh-hant/p/%E4%BD%B3%E8%83%BD%E9%A3%9F%E7%89%A9%E4%BF%9D%E9%AE%AE%E8%A2%8B%E5%A4%A7%E8%A2%8B%20100EA/i/101347619.html</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>https://img.rtacdn-os.com/20260109/7a92b621-a10c-3303-aa76-8d1252654093</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -28312,35 +28494,45 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>食物保鮮密實袋（中）</t>
+          <t>TOP-Z 博仕牌 食物保鮮密實袋[中碼] (50個裝) (19 x 20cm) ︳保鮮袋 密實袋 廚房用品 雙重夾鏈 安全 食物保存</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
+          <t>（頁面未列型號）</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
           <t>50 個，19×20cm</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>拉鏈密實袋</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>$20（原價 $22）</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>友和 YOHO</t>
         </is>
       </c>
-      <c r="H19" s="12" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>https://www.yohohongkong.com/zh-hk/product/335649</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>https://store.yohohongkong.com/mkp/gallery/goods/images/c9233ce4-67d2-469d-91bc-67e36bd0b665_mkp_image.webp</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>價錢來自搜尋結果卡</t>
         </is>
@@ -28359,35 +28551,45 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>REK-001H 保溫袋</t>
+          <t>黑色保溫袋</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
+          <t>REK-001H-BK</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
           <t>24×11×14.5cm</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>配合 Thermos 食物罐使用</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>$218</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>THERMOS HK 官網</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>https://www.thermos.com.hk/p/REK-001H-BK</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/XpZce875ssw9NxZWKuW0A.png</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -28402,35 +28604,45 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Zuma 冷藏袋</t>
+          <t>Packit 冰酷 經典2022 Zuma 系列冷藏袋 5L 保冷袋 保冰袋 母乳袋 行動式摺疊冰箱 藍色</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
+          <t>Zuma 5L</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
           <t>5L</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>袋身內置凝膠，冷凍 12 小時後毋須冰袋</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>$285（原價 $325）</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>友和 YOHO</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>https://www.yohohongkong.com/zh-hk/product/80121</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>https://store.yohohongkong.com/mkp/gallery/goods/images/416_108357_81990840.jpg</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -28445,60 +28657,91 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>HUGEL VITC-20 真空隔熱保溫箱</t>
+          <t>IRIS OHYAMA 愛麗思 HUGEL 20L VITC 真空隔熱保溫箱 炭灰色 VITC-20 香港行貨</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
+          <t>VITC-20</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
           <t>20L</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>真空隔熱，保冷保溫兩用</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>$899（原價 $1,149）</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>友和 YOHO</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>https://www.yohohongkong.com/zh-hk/product/226394</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr"/>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>https://www1.yohohongkong.com/images/202507/goods_img/226394_P_1753153737904.png</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:K22"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/thermal-lunchbox-blog/保溫保鮮餐具_KW分類_2026-10-28.xlsx
+++ b/thermal-lunchbox-blog/保溫保鮮餐具_KW分類_2026-10-28.xlsx
@@ -27996,54 +27996,50 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>VVU&amp;CCO 物克</t>
+          <t>Rasonic 樂信</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>VVU&amp;CCO 物克 充電式便攜加熱飯盒</t>
+          <t>迷你雙層蒸煮盒</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>（頁面未列型號）</t>
+          <t>RSB-BV212S</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>未有標示</t>
+          <t>官方未列容量</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>可充電；多段溫度；內膽可拆</t>
+          <t>270W；220–240V；304 不鏽鋼單格及雙格盒；過熱及缺水自動關機</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>$415（原價 $510）</t>
+          <t>$318</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>友和 YOHO</t>
+          <t>信興電器官網（Rasonic 香港代理）</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>https://www.yohohongkong.com/zh-hk/product/492130</t>
+          <t>https://www.shew.com.hk/chinese/brand/rasonic/kitchen/mini-double-deck-steam-box/rsb-bv212s.aspx</t>
         </is>
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>https://store.yohohongkong.com/mkp/gallery/goods/images/a3c71d28-845f-4c49-93da-ffd505ad7c8c_mkp_image.webp</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>頁面未列容量</t>
-        </is>
-      </c>
+          <t>https://www.shew.com.hk/usm.ashx/e/9067B0382A99E77958BDE12B0943EAB4F251E5ADB8BD3DA4564A762B6F6D8ED9B737F584C7D5589FEFDD02C6B3E7DE8C6E5B77CD1793B502EED3A7666A4B473E</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">

--- a/thermal-lunchbox-blog/保溫保鮮餐具_KW分類_2026-10-28.xlsx
+++ b/thermal-lunchbox-blog/保溫保鮮餐具_KW分類_2026-10-28.xlsx
@@ -27487,7 +27487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -27668,7 +27668,11 @@
           <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/df12/c9bb/ad1d/VcMtgUYaVG20250424142658_1200.png</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -27721,7 +27725,11 @@
           <t>https://assets.omniwe.com/4jt453fJsHDBJXQi6jkPD.png</t>
         </is>
       </c>
-      <c r="K4" s="6" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -27774,7 +27782,11 @@
           <t>https://assets.omniwe.com/OTxKkk94WVhg9k0HSwtUp.png</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -27880,7 +27892,11 @@
           <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/4781/e49e/b2c5/jxwZGMsQSN20250424145612_1200.png</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -28692,6 +28708,1260 @@
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>象印 Zojirushi</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>0.64L不銹鋼保溫飯壺 (小盛)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>SL-MEE07</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>飯盒 0.31L（約 1.5 碗飯）＋菜盒 0.33L</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 53°C 以上、保冷 11°C 以下；內容器可微波（蓋子除外）；約 12.5 × 11 × 16cm；連手提袋約 0.7kg</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>官網未列價錢</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>象印香港官網（象印保溫飯壺（官網「保溫便當」系列 5 款））</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=7&amp;pid=153</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/20173610044711.jpg</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>象印 Zojirushi</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>0.84L不銹鋼保溫飯壺 (並盛)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>SL-NC09</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>飯盒 0.31L（約 1.5 碗飯）＋菜盒 0.33L＋湯盒 0.2L</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 65°C 以上；飯盒、菜盒、湯盒均可微波（蓋子除外）；約 12.5 × 11 × 20.5cm；連手提袋約 0.9kg</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>官網未列價錢（參考：HKTVmall $299，原價 $428，2026 年 10 月 28 日記錄）</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>象印香港官網（象印保溫飯壺（官網「保溫便當」系列 5 款））</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=7&amp;pid=154</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/20172914503313.jpg</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>象印 Zojirushi</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>1.27L 不銹鋼保溫飯壺 (大盛)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>SL-GH18</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>飯盒 0.59L（約 3 碗飯）＋菜盒 0.4L＋湯盒 0.28L</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫（飯器）69°C 以上；內容器銀離子（Ag+）抗菌處理；可微波（蓋子除外）；約 15 × 13.5 × 21cm；約 1kg</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>官網未列價錢</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>象印香港官網（象印保溫飯壺（官網「保溫便當」系列 5 款））</t>
+        </is>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=7&amp;pid=267</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/201822010503939.jpg</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>象印 Zojirushi</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>1.47L不銹鋼保溫飯壺 (特盛)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>SL-XE20</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>飯盒 0.79L（約 4 碗飯）＋菜盒 0.4L＋湯盒 0.28L</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫（飯器）71°C 以上；內容器銀離子（Ag+）抗菌處理；可微波（蓋子除外）；約 15 × 13.5 × 23.5cm；約 1.1kg</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>官網未列價錢</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>象印香港官網（象印保溫飯壺（官網「保溫便當」系列 5 款））</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=7&amp;pid=260</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/201811009272020.jpg</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>象印 Zojirushi</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>1.23L不銹鋼保溫飯壺 (菜盒2個)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>SL-JAF14</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>飯盒 0.45L（約 2.5 碗飯）＋大菜盒 0.3L＋小菜盒 0.2L＋湯盒 0.28L</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫（飯器）67°C 以上；飯盒、菜盒、湯盒均可微波（蓋子除外）；約 15 × 13.5 × 22cm；連手提袋約 1.1kg</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>官網未列價錢</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>象印香港官網（象印保溫飯壺（官網「保溫便當」系列 5 款））</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=7&amp;pid=316</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/2020123012122818.jpg</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>象印 Zojirushi</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>0.3L 童用不鏽鋼真空保溫杯 (吸管型)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>SQ-DA30E</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>0.32L（11oz）</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 75°C 以上、保冷 9°C 以下；SUS304 不銹鋼；約 11 × 7 × 17cm；約 0.191kg</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>官網未列價錢</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>象印香港官網（象印兒童保溫壺（官網「兒童壺」系列 4 款））</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=6&amp;tid=20&amp;pid=340</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/202681112102420.jpg</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>象印 Zojirushi</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>0.5L不銹鋼兒童壺</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>SD-CAE50</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>0.5L</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>保冷 6 小時 9°C 以下（官網未列保溫效力）；單觸式瓶蓋；內部防黏塗層</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>官網未列價錢</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>象印香港官網（象印兒童保溫壺（官網「兒童壺」系列 4 款））</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=6&amp;tid=20&amp;pid=261</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/201821411034834.jpg</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>象印 Zojirushi</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>0.62L 兩用保溫保冷兒童壺</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SP-JB06</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>0.62L</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 77°C 以上、保冷 8°C 以下；兩種瓶蓋（直飲型、水杯型）；雙層防黏塗層</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>官網未列價錢</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>象印香港官網（象印兒童保溫壺（官網「兒童壺」系列 4 款））</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=6&amp;tid=20&amp;pid=286</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/20195211000219.jpg</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>象印 Zojirushi</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>0.45L可攜帶兩用兒童壺</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>SC-ZT45</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>0.45L</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>保溫 6 小時 72°C 以上（24 小時 40°C 以上）；保冷 6 小時 9°C 以下（杯蓋）／10°C 以下（吸管蓋）</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>官網未列價錢</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>象印香港官網（象印兒童保溫壺（官網「兒童壺」系列 4 款））</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=6&amp;tid=20&amp;pid=240</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/201851418034330.jpg</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 Tiger</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 - 真空保溫飯盒套裝 LWU-B200 1.48L 銀灰色 | 保溫便當盒 | 食物盒</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>LWU-B200</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>1.48L（飯盒 0.8L＋餸盒 0.34L＋湯盒 0.27L）</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 72°C 以上；約 15.0 × 14.7 × 23.6cm；約 1.0kg；附專用袋及筷子</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>$348（原價 $478）</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌真空保溫飯盒（3 款））</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hktvmall.com/p/H5036001_S_LWU-B200-SE</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/87d6/0241/378b/dthcTadYds20250424144218_1200.png</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 Tiger</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 - 真空保溫飯盒套裝 LWU-F200 1.48L 銀灰色 | 保溫便當盒 | 食物盒</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>LWU-F200</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>1.48L（飯盒 0.61L＋餸盒 0.30L × 2＋湯盒 0.27L）</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 72°C 以上；約 15 × 14.7 × 25.6cm；約 1.4kg；附專用提袋及筷子</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>$466（原價 $518）</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌真空保溫飯盒（3 款））</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hktvmall.com/p/H5036001_S_LWU-F200-SE</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/d690/7cbf/6614/rfnIxulppV20250424144344_1200.png</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>550毫升保溫便當盒 - 灰色 (附提袋)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>JBY-550-DGY</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>550ml（300ml 食物罐＋250ml 食物儲存盒）</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 56°C 以上、保冷 12°C 以下（連提袋保溫 58°C 以上）；約 9 × 9.5 × 17cm；連提袋約 400g</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>$318</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「食物罐／便當盒」（膳魔師保溫便當盒（3 款））</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/992c0865-b286-4f70-b340-0722280bb636</t>
+        </is>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/bCqhPw3m7Oyf5EsFn3fDf.jpeg</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>保溫飯盒／保溫便當盒</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>1.6公升真空保温便當盒</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>JLS-1601F-CGY</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>1.6L</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>官網未列保溫效力；約 14.5 × 12 × 25cm；約 1.1kg</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>$498</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「食物罐／便當盒」（膳魔師保溫便當盒（3 款））</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/0e80795c-f502-4580-b9f4-34f91d888c59</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/MN5DyJkzAFnj-7gZYLCzn.png</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 Tiger</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 - 不銹鋼真空保溫湯杯 MCA-C025 250ml 天藍色 | 迷你燜燒杯 | 食物罐</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>MCA-C025</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>0.25L</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>保溫 1 小時 83°C 以上、6 小時 56°C 以上；保冷 6 小時 12°C 以下；約 7.5 × 7.5 × 10.9cm；約 0.17kg</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>$188（原價 $268）</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hktvmall.com/p/H5036001_S_MCA-C025-AS</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/c999/270c/0d43/RmIDhFFcIu20250424160030_1200.png</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 Tiger</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 - 不銹鋼真空燜燒杯 MKL-W040 400ml 雲朵藍 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>MKL-W040</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>0.4L</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 61°C 以上、保冷 10°C 以下；約 9.9 × 9.9 × 12.8cm；約 0.34kg</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>$348（原價 $388）</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hktvmall.com/p/H5036001_S_MKL-W040-AL</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/6aeb/1ac5/8a14/HxKYFxLBfu20251009121402_1200.png</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 Tiger</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 - 不銹鋼真空燜燒杯 MCJ-K050 500ml 森林沁綠 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>MCJ-K050</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>0.5L</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 62°C 以上、保冷 10°C 以下；約 9.9 × 9.9 × 11.6cm；約 0.33kg</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>$268（原價 $428）</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hktvmall.com/p/H5036001_S_MCJ-K050-GZ</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/92af/df01/7e42/UotVpppCwn20250424145017_1200.png</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 Tiger</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 - 不銹鋼真空燜燒杯 MKL-W075 750ml 雲朵藍 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>MKL-W075</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>0.75L</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 73°C 以上、保冷 8°C 以下；約 9.9 × 9.9 × 17.9cm；約 0.41kg</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>$388（原價 $428）</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+        </is>
+      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hktvmall.com/p/H5036001_S_MKL-W075-AL</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/9ecd/ae90/dd7e/DHIJAcPFeI20260313144144_1200.png</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Miffy 300毫升真空食物罐</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>JBU-302B-LTG</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 53°C 以上、保冷 12°C 以下；約 9.5 × 9.5 × 11cm；約 300g</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>$358</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/7249d02b-434e-4eee-9af5-68cb1bb2f601</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/J2oHoS5mHdRQCdIpDBgRK.jpeg</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>400毫升真空食物罐 - 象牙白</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>JED-400-IV</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>400ml</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 60°C 以上、保冷 11°C 以下；約 9.5 × 9.5 × 12.5cm；約 300g</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>$378</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/880d0dd3-0776-4f18-8322-0e1149723bdb</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/zbV81xiA7TNRdfA9oVtPg.jpeg</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>500毫升真空燜燒罐 - 白色</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>JBT-500-WH</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 61°C 以上、保冷 11°C 以下；約 10 × 10 × 13.5cm；約 300g</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>$398</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/e52de0f9-8de4-4efa-b2df-7984db921136</t>
+        </is>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/so9ZARfzMVgplAeZWng-O.png</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>500毫升真空燜燒罐 - 象牙白</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>JED-500-IV</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>保溫 63°C 以上、保冷 11°C 以下（官網未註明時數）；約 10 × 10 × 13.5cm；約 300g</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>$398</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+        </is>
+      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/d85476ab-aaa7-4519-9488-580fe0a4ee25</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/kHjiYFwtczXI6KSOure5O.jpeg</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>500毫升真空燜燒罐 - 銀色</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>JCU-500-SBK</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>官網列明 6 小時保溫 53°C 以上、保冷 3°C 以下；口徑 7.5cm；約 9 × 9 × 16cm；約 350g</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>$328</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/edeb099a-5799-42df-83b1-a4a3593f6e32</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/Ug1FIhIoIAFOJ0KUk8YQB.png</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K22"/>
@@ -28738,6 +30008,50 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/thermal-lunchbox-blog/保溫保鮮餐具_KW分類_2026-10-28.xlsx
+++ b/thermal-lunchbox-blog/保溫保鮮餐具_KW分類_2026-10-28.xlsx
@@ -27487,7 +27487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -29225,52 +29225,52 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>保溫飯盒／保溫便當盒</t>
+          <t>燜燒壺／燜燒杯／湯壺</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>虎牌 Tiger</t>
+          <t>象印 Zojirushi</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>虎牌 - 真空保溫飯盒套裝 LWU-B200 1.48L 銀灰色 | 保溫便當盒 | 食物盒</t>
+          <t>0.3L不銹鋼燜燒杯 一體式中栓</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>LWU-B200</t>
+          <t>SW-KA30</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>1.48L（飯盒 0.8L＋餸盒 0.34L＋湯盒 0.27L）</t>
+          <t>300ml</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>6 小時保溫 72°C 以上；約 15.0 × 14.7 × 23.6cm；約 1.0kg；附專用袋及筷子</t>
+          <t>6 小時保溫 58°C 以上、保冷 10°C 以下；約 9.5 × 9.5 × 11cm；約 0.29kg</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>$348（原價 $478）</t>
+          <t>官網未列價錢</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌真空保溫飯盒（3 款））</t>
+          <t>象印香港官網（象印燜燒杯（官網「燜燒杯」系列 7 款））</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>https://www.hktvmall.com/p/H5036001_S_LWU-B200-SE</t>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=11&amp;pid=350</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/87d6/0241/378b/dthcTadYds20250424144218_1200.png</t>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/202341418082233.jpg</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -29282,52 +29282,52 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>保溫飯盒／保溫便當盒</t>
+          <t>燜燒壺／燜燒杯／湯壺</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>虎牌 Tiger</t>
+          <t>象印 Zojirushi</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>虎牌 - 真空保溫飯盒套裝 LWU-F200 1.48L 銀灰色 | 保溫便當盒 | 食物盒</t>
+          <t>0.4L不銹鋼燜燒杯 一體式中栓</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>LWU-F200</t>
+          <t>SW-KA40</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>1.48L（飯盒 0.61L＋餸盒 0.30L × 2＋湯盒 0.27L）</t>
+          <t>400ml</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>6 小時保溫 72°C 以上；約 15 × 14.7 × 25.6cm；約 1.4kg；附專用提袋及筷子</t>
+          <t>6 小時保溫 64°C 以上、保冷 9°C 以下；約 9.5 × 9.5 × 12.5cm；約 0.32kg</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>$466（原價 $518）</t>
+          <t>官網未列價錢</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌真空保溫飯盒（3 款））</t>
+          <t>象印香港官網（象印燜燒杯（官網「燜燒杯」系列 7 款））</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>https://www.hktvmall.com/p/H5036001_S_LWU-F200-SE</t>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=11&amp;pid=349</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/d690/7cbf/6614/rfnIxulppV20250424144344_1200.png</t>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/202341418063011.jpg</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -29339,52 +29339,52 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>保溫飯盒／保溫便當盒</t>
+          <t>燜燒壺／燜燒杯／湯壺</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>膳魔師 Thermos</t>
+          <t>象印 Zojirushi</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>550毫升保溫便當盒 - 灰色 (附提袋)</t>
+          <t>0.52L不銹鋼燜燒杯 一體式中栓</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>JBY-550-DGY</t>
+          <t>SW-KA52/52H</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>550ml（300ml 食物罐＋250ml 食物儲存盒）</t>
+          <t>520ml</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>6 小時保溫 56°C 以上、保冷 12°C 以下（連提袋保溫 58°C 以上）；約 9 × 9.5 × 17cm；連提袋約 400g</t>
+          <t>6 小時保溫 67°C 以上、保冷 9°C 以下；約 9.5 × 9.5 × 14.5cm；約 0.36kg</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>$318</t>
+          <t>官網未列價錢</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>THERMOS 香港官網「食物罐／便當盒」（膳魔師保溫便當盒（3 款））</t>
+          <t>象印香港官網（象印燜燒杯（官網「燜燒杯」系列 7 款））</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>https://www.thermos.com.hk/product/992c0865-b286-4f70-b340-0722280bb636</t>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=11&amp;pid=348</t>
         </is>
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>https://assets.omniwe.com/bCqhPw3m7Oyf5EsFn3fDf.jpeg</t>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/202341417563813.jpg</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -29396,52 +29396,52 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>保溫飯盒／保溫便當盒</t>
+          <t>燜燒壺／燜燒杯／湯壺</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>膳魔師 Thermos</t>
+          <t>象印 Zojirushi</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>1.6公升真空保温便當盒</t>
+          <t>0.75L不銹鋼燜燒杯 一體式中栓</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>JLS-1601F-CGY</t>
+          <t>SW-KA75H</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1.6L</t>
+          <t>750ml</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>官網未列保溫效力；約 14.5 × 12 × 25cm；約 1.1kg</t>
+          <t>6 小時保溫 73°C 以上、保冷 8°C 以下；約 9.5 × 9.5 × 18.5cm；約 0.42kg</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>$498</t>
+          <t>官網未列價錢</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>THERMOS 香港官網「食物罐／便當盒」（膳魔師保溫便當盒（3 款））</t>
+          <t>象印香港官網（象印燜燒杯（官網「燜燒杯」系列 7 款））</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>https://www.thermos.com.hk/product/0e80795c-f502-4580-b9f4-34f91d888c59</t>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=11&amp;pid=347</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>https://assets.omniwe.com/MN5DyJkzAFnj-7gZYLCzn.png</t>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/202341417192533.jpg</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -29458,47 +29458,47 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>虎牌 Tiger</t>
+          <t>象印 Zojirushi</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>虎牌 - 不銹鋼真空保溫湯杯 MCA-C025 250ml 天藍色 | 迷你燜燒杯 | 食物罐</t>
+          <t>0.35L不銹鋼燜燒杯</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>MCA-C025</t>
+          <t>SW-EAE35</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>0.25L</t>
+          <t>0.35L</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>保溫 1 小時 83°C 以上、6 小時 56°C 以上；保冷 6 小時 12°C 以下；約 7.5 × 7.5 × 10.9cm；約 0.17kg</t>
+          <t>6 小時保溫 57°C 以上、保冷 12°C 以下；6.5cm 口徑；SUS304 不銹鋼內容器</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>$188（原價 $268）</t>
+          <t>官網未列價錢</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+          <t>象印香港官網（象印燜燒杯（官網「燜燒杯」系列 7 款））</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>https://www.hktvmall.com/p/H5036001_S_MCA-C025-AS</t>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=11&amp;pid=158</t>
         </is>
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/c999/270c/0d43/RmIDhFFcIu20250424160030_1200.png</t>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/20213115035714.jpg</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -29515,47 +29515,47 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>虎牌 Tiger</t>
+          <t>象印 Zojirushi</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>虎牌 - 不銹鋼真空燜燒杯 MKL-W040 400ml 雲朵藍 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
+          <t>0.5L不銹鋼燜燒杯</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>MKL-W040</t>
+          <t>SW-EAE50</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>0.4L</t>
+          <t>0.5L</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>6 小時保溫 61°C 以上、保冷 10°C 以下；約 9.9 × 9.9 × 12.8cm；約 0.34kg</t>
+          <t>6 小時保溫 64°C 以上、保冷 10°C 以下；6.5cm 口徑；SUS304 不銹鋼內容器</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>$348（原價 $388）</t>
+          <t>官網未列價錢（參考：HKTVmall $269，原價 $278，2026 年 10 月 28 日記錄）</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+          <t>象印香港官網（象印燜燒杯（官網「燜燒杯」系列 7 款））</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>https://www.hktvmall.com/p/H5036001_S_MKL-W040-AL</t>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=11&amp;pid=160</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/6aeb/1ac5/8a14/HxKYFxLBfu20251009121402_1200.png</t>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/20213114590611.jpg</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -29572,47 +29572,47 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>虎牌 Tiger</t>
+          <t>象印 Zojirushi</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>虎牌 - 不銹鋼真空燜燒杯 MCJ-K050 500ml 森林沁綠 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
+          <t>0.75L不銹鋼燜燒杯</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>MCJ-K050</t>
+          <t>SW-FCE75</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>0.5L</t>
+          <t>0.75L</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>6 小時保溫 62°C 以上、保冷 10°C 以下；約 9.9 × 9.9 × 11.6cm；約 0.33kg</t>
+          <t>6 小時保溫 71°C 以上、保冷 8°C 以下；7cm 口徑；SUS304 不銹鋼內容器</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>$268（原價 $428）</t>
+          <t>官網未列價錢</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+          <t>象印香港官網（象印燜燒杯（官網「燜燒杯」系列 7 款））</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>https://www.hktvmall.com/p/H5036001_S_MCJ-K050-GZ</t>
+          <t>https://www.zojirushi.com.hk/hkproductsview.php?oid=11&amp;pid=168</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/92af/df01/7e42/UotVpppCwn20250424145017_1200.png</t>
+          <t>https://www.zojirushi.com.hk/UPFILE/ProductPic/20213114521236.jpg</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -29624,7 +29624,7 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>燜燒壺／燜燒杯／湯壺</t>
+          <t>保溫飯盒／保溫便當盒</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -29634,42 +29634,42 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>虎牌 - 不銹鋼真空燜燒杯 MKL-W075 750ml 雲朵藍 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
+          <t>虎牌 - 真空保溫飯盒套裝 LWU-B200 1.48L 銀灰色 | 保溫便當盒 | 食物盒</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>MKL-W075</t>
+          <t>LWU-B200</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>0.75L</t>
+          <t>1.48L（飯盒 0.8L＋餸盒 0.34L＋湯盒 0.27L）</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>6 小時保溫 73°C 以上、保冷 8°C 以下；約 9.9 × 9.9 × 17.9cm；約 0.41kg</t>
+          <t>6 小時保溫 72°C 以上；約 15.0 × 14.7 × 23.6cm；約 1.0kg；附專用袋及筷子</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>$388（原價 $428）</t>
+          <t>$348（原價 $478）</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌真空保溫飯盒（3 款））</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>https://www.hktvmall.com/p/H5036001_S_MKL-W075-AL</t>
+          <t>https://www.hktvmall.com/p/H5036001_S_LWU-B200-SE</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/9ecd/ae90/dd7e/DHIJAcPFeI20260313144144_1200.png</t>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/87d6/0241/378b/dthcTadYds20250424144218_1200.png</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -29681,52 +29681,52 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>燜燒壺／燜燒杯／湯壺</t>
+          <t>保溫飯盒／保溫便當盒</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>膳魔師 Thermos</t>
+          <t>虎牌 Tiger</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Miffy 300毫升真空食物罐</t>
+          <t>虎牌 - 真空保溫飯盒套裝 LWU-F200 1.48L 銀灰色 | 保溫便當盒 | 食物盒</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>JBU-302B-LTG</t>
+          <t>LWU-F200</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>1.48L（飯盒 0.61L＋餸盒 0.30L × 2＋湯盒 0.27L）</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>6 小時保溫 53°C 以上、保冷 12°C 以下；約 9.5 × 9.5 × 11cm；約 300g</t>
+          <t>6 小時保溫 72°C 以上；約 15 × 14.7 × 25.6cm；約 1.4kg；附專用提袋及筷子</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>$358</t>
+          <t>$466（原價 $518）</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌真空保溫飯盒（3 款））</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>https://www.thermos.com.hk/product/7249d02b-434e-4eee-9af5-68cb1bb2f601</t>
+          <t>https://www.hktvmall.com/p/H5036001_S_LWU-F200-SE</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://assets.omniwe.com/J2oHoS5mHdRQCdIpDBgRK.jpeg</t>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/d690/7cbf/6614/rfnIxulppV20250424144344_1200.png</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -29738,7 +29738,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>燜燒壺／燜燒杯／湯壺</t>
+          <t>保溫飯盒／保溫便當盒</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -29748,42 +29748,42 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>400毫升真空食物罐 - 象牙白</t>
+          <t>550毫升保溫便當盒 - 灰色 (附提袋)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>JED-400-IV</t>
+          <t>JBY-550-DGY</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>400ml</t>
+          <t>550ml（300ml 食物罐＋250ml 食物儲存盒）</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>6 小時保溫 60°C 以上、保冷 11°C 以下；約 9.5 × 9.5 × 12.5cm；約 300g</t>
+          <t>6 小時保溫 56°C 以上、保冷 12°C 以下（連提袋保溫 58°C 以上）；約 9 × 9.5 × 17cm；連提袋約 400g</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>$378</t>
+          <t>$318</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+          <t>THERMOS 香港官網「食物罐／便當盒」（膳魔師保溫便當盒（3 款））</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>https://www.thermos.com.hk/product/880d0dd3-0776-4f18-8322-0e1149723bdb</t>
+          <t>https://www.thermos.com.hk/product/992c0865-b286-4f70-b340-0722280bb636</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>https://assets.omniwe.com/zbV81xiA7TNRdfA9oVtPg.jpeg</t>
+          <t>https://assets.omniwe.com/bCqhPw3m7Oyf5EsFn3fDf.jpeg</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -29795,7 +29795,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>燜燒壺／燜燒杯／湯壺</t>
+          <t>保溫飯盒／保溫便當盒</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -29805,42 +29805,42 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>500毫升真空燜燒罐 - 白色</t>
+          <t>1.6公升真空保温便當盒</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>JBT-500-WH</t>
+          <t>JLS-1601F-CGY</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>1.6L</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>6 小時保溫 61°C 以上、保冷 11°C 以下；約 10 × 10 × 13.5cm；約 300g</t>
+          <t>官網未列保溫效力；約 14.5 × 12 × 25cm；約 1.1kg</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>$398</t>
+          <t>$498</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+          <t>THERMOS 香港官網「食物罐／便當盒」（膳魔師保溫便當盒（3 款））</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>https://www.thermos.com.hk/product/e52de0f9-8de4-4efa-b2df-7984db921136</t>
+          <t>https://www.thermos.com.hk/product/0e80795c-f502-4580-b9f4-34f91d888c59</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>https://assets.omniwe.com/so9ZARfzMVgplAeZWng-O.png</t>
+          <t>https://assets.omniwe.com/MN5DyJkzAFnj-7gZYLCzn.png</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -29857,47 +29857,47 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>膳魔師 Thermos</t>
+          <t>虎牌 Tiger</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>500毫升真空燜燒罐 - 象牙白</t>
+          <t>虎牌 - 不銹鋼真空保溫湯杯 MCA-C025 250ml 天藍色 | 迷你燜燒杯 | 食物罐</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>JED-500-IV</t>
+          <t>MCA-C025</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>0.25L</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>保溫 63°C 以上、保冷 11°C 以下（官網未註明時數）；約 10 × 10 × 13.5cm；約 300g</t>
+          <t>保溫 1 小時 83°C 以上、6 小時 56°C 以上；保冷 6 小時 12°C 以下；約 7.5 × 7.5 × 10.9cm；約 0.17kg</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>$398</t>
+          <t>$188（原價 $268）</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>https://www.thermos.com.hk/product/d85476ab-aaa7-4519-9488-580fe0a4ee25</t>
+          <t>https://www.hktvmall.com/p/H5036001_S_MCA-C025-AS</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://assets.omniwe.com/kHjiYFwtczXI6KSOure5O.jpeg</t>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/c999/270c/0d43/RmIDhFFcIu20250424160030_1200.png</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -29914,50 +29914,449 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
+          <t>虎牌 Tiger</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 - 不銹鋼真空燜燒杯 MKL-W040 400ml 雲朵藍 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>MKL-W040</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>0.4L</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 61°C 以上、保冷 10°C 以下；約 9.9 × 9.9 × 12.8cm；約 0.34kg</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>$348（原價 $388）</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hktvmall.com/p/H5036001_S_MKL-W040-AL</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/6aeb/1ac5/8a14/HxKYFxLBfu20251009121402_1200.png</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 Tiger</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 - 不銹鋼真空燜燒杯 MCJ-K050 500ml 森林沁綠 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>MCJ-K050</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>0.5L</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 62°C 以上、保冷 10°C 以下；約 9.9 × 9.9 × 11.6cm；約 0.33kg</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>$268（原價 $428）</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hktvmall.com/p/H5036001_S_MCJ-K050-GZ</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/92af/df01/7e42/UotVpppCwn20250424145017_1200.png</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 Tiger</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>虎牌 - 不銹鋼真空燜燒杯 MKL-W075 750ml 雲朵藍 | 食物罐 | 保溫飯盒便當盒 | 食物儲存盒 | 野餐露營便當盒 | 保溫瓶罐 | 保冷壼</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>MKL-W075</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>0.75L</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 73°C 以上、保冷 8°C 以下；約 9.9 × 9.9 × 17.9cm；約 0.41kg</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>$388（原價 $428）</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>HKTVmall Tiger 虎牌官方旗艦店（虎牌燜燒杯／湯杯（5 款））</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>https://www.hktvmall.com/p/H5036001_S_MKL-W075-AL</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>https://cdn-media.hktvmall.com/hktv-mms/HKTV/mms/uploadProductImage/9ecd/ae90/dd7e/DHIJAcPFeI20260313144144_1200.png</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
           <t>膳魔師 Thermos</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Miffy 300毫升真空食物罐</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>JBU-302B-LTG</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 53°C 以上、保冷 12°C 以下；約 9.5 × 9.5 × 11cm；約 300g</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>$358</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+        </is>
+      </c>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/7249d02b-434e-4eee-9af5-68cb1bb2f601</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/J2oHoS5mHdRQCdIpDBgRK.jpeg</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>400毫升真空食物罐 - 象牙白</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>JED-400-IV</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>400ml</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 60°C 以上、保冷 11°C 以下；約 9.5 × 9.5 × 12.5cm；約 300g</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>$378</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/880d0dd3-0776-4f18-8322-0e1149723bdb</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/zbV81xiA7TNRdfA9oVtPg.jpeg</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>500毫升真空燜燒罐 - 白色</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>JBT-500-WH</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>6 小時保溫 61°C 以上、保冷 11°C 以下；約 10 × 10 × 13.5cm；約 300g</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>$398</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/e52de0f9-8de4-4efa-b2df-7984db921136</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/so9ZARfzMVgplAeZWng-O.png</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>500毫升真空燜燒罐 - 象牙白</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>JED-500-IV</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>保溫 63°C 以上、保冷 11°C 以下（官網未註明時數）；約 10 × 10 × 13.5cm；約 300g</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>$398</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>https://www.thermos.com.hk/product/d85476ab-aaa7-4519-9488-580fe0a4ee25</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>https://assets.omniwe.com/kHjiYFwtczXI6KSOure5O.jpeg</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>Slider 顯示</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>燜燒壺／燜燒杯／湯壺</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>膳魔師 Thermos</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>500毫升真空燜燒罐 - 銀色</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>JCU-500-SBK</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>500ml</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <t>官網列明 6 小時保溫 53°C 以上、保冷 3°C 以下；口徑 7.5cm；約 9 × 9 × 16cm；約 350g</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G51" s="6" t="inlineStr">
         <is>
           <t>$328</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>THERMOS 香港官網「燜燒罐」及「食物罐／便當盒」（膳魔師真空食物罐／燜燒罐（6 款））</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>https://www.thermos.com.hk/product/edeb099a-5799-42df-83b1-a4a3593f6e32</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>https://assets.omniwe.com/Ug1FIhIoIAFOJ0KUk8YQB.png</t>
         </is>
       </c>
-      <c r="K44" s="6" t="inlineStr">
+      <c r="K51" s="6" t="inlineStr">
         <is>
           <t>Slider 顯示</t>
         </is>
@@ -30052,6 +30451,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
